--- a/Resources/O3/EMR-DHIS2 Tracker O3 Maternal Mapping.xlsx
+++ b/Resources/O3/EMR-DHIS2 Tracker O3 Maternal Mapping.xlsx
@@ -35,12 +35,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Tenderness [APH CHART]</t>
+          <t xml:space="preserve">Abdominal Pain [APH CHART]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Tenderness APH</t>
+          <t xml:space="preserve">Abdominal Pain APH</t>
         </is>
       </c>
     </row>
@@ -52,12 +52,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">APH event date [APH CHART]</t>
+          <t xml:space="preserve">Abdominal Tenderness [APH CHART]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">APH event date</t>
+          <t xml:space="preserve">Abdominal Tenderness APH</t>
         </is>
       </c>
     </row>
@@ -69,12 +69,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIOPHYSICAL PROFILE [APH CHART]</t>
+          <t xml:space="preserve">APH event date [APH CHART]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIOPHYSICAL PROFILE APH</t>
+          <t xml:space="preserve">APH event date</t>
         </is>
       </c>
     </row>
@@ -86,454 +86,454 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal bleeding [APH CHART]</t>
+          <t xml:space="preserve">BIOPHYSICAL PROFILE [APH CHART]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal bleeding APH</t>
+          <t xml:space="preserve">BIOPHYSICAL PROFILE APH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood pressure (diastolic) [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">BP (diastolic) [APH CHART]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood pressure diastolic DMP</t>
+          <t xml:space="preserve">BP diastolic APH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood pressure (Systolic) [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">BP (systolic) [APH CHART]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood pressure Systolic DMP</t>
+          <t xml:space="preserve">BP systolic APH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of admission [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">Date [APH CHART]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of admission DMP</t>
+          <t xml:space="preserve">Date APH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph Entry [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">FHB (Fetal Heart Beat) [APH CHART]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring Partograph event date</t>
+          <t xml:space="preserve">FHB APH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fetal Heart Rate [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">HCT [APH CHART]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fetal Heart Rate DMP</t>
+          <t xml:space="preserve">HCT APH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein in Urine [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">PR [APH CHART]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protein in Urine DMP</t>
+          <t xml:space="preserve">PR APH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruptured Membranes [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">RR [APH CHART]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruptured Membranes DMP</t>
+          <t xml:space="preserve">RR APH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery Monitoring partograph</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Admission [Delivery Monitoring partograph]</t>
+          <t xml:space="preserve">Temp [APH CHART]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Admission DMP</t>
+          <t xml:space="preserve">Temp APH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min [Delivery summary]</t>
+          <t xml:space="preserve">Time [APH CHART]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min</t>
+          <t xml:space="preserve">Time APH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">APH CHART</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 2 [Delivery summary]</t>
+          <t xml:space="preserve">Vaginal bleeding [APH CHART]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 2</t>
+          <t xml:space="preserve">Vaginal bleeding APH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 3 [Delivery summary]</t>
+          <t xml:space="preserve">Amniotic fluid [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 3</t>
+          <t xml:space="preserve">Amniotic fluid DMP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 4 [Delivery summary]</t>
+          <t xml:space="preserve">Blood pressure (diastolic) [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 10th min newborn 4</t>
+          <t xml:space="preserve">Blood pressure diastolic DMP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min [Delivery summary]</t>
+          <t xml:space="preserve">Blood pressure (Systolic) [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min</t>
+          <t xml:space="preserve">Blood pressure Systolic DMP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 2 [Delivery summary]</t>
+          <t xml:space="preserve">Cervix (cm) [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 2</t>
+          <t xml:space="preserve">Cervix cm DMP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 3 [Delivery summary]</t>
+          <t xml:space="preserve">Contraction (per 10 min) [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 3</t>
+          <t xml:space="preserve">Contraction DMP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 4 [Delivery summary]</t>
+          <t xml:space="preserve">Date of admission [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 1st min newborn 4</t>
+          <t xml:space="preserve">Date of admission DMP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min [Delivery summary]</t>
+          <t xml:space="preserve">Delivery Monitoring partograph Entry [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min</t>
+          <t xml:space="preserve">Delivery Monitoring Partograph event date</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 2 [Delivery summary]</t>
+          <t xml:space="preserve">Fetal Heart Rate [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 2</t>
+          <t xml:space="preserve">Fetal Heart Rate DMP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 3 [Delivery summary]</t>
+          <t xml:space="preserve">Hours [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 3</t>
+          <t xml:space="preserve">Hours DMP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 4 [Delivery summary]</t>
+          <t xml:space="preserve">Maternal Pulse [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apgar Score 5th min newborn 4</t>
+          <t xml:space="preserve">Maternal Pulse DMP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 2: [Delivery summary]</t>
+          <t xml:space="preserve">Minutes [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 2</t>
+          <t xml:space="preserve">After How many minutes Featl Heart Rate Measured</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 3: [Delivery summary]</t>
+          <t xml:space="preserve">Moulding [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 3</t>
+          <t xml:space="preserve">Moulding DMP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 4: [Delivery summary]</t>
+          <t xml:space="preserve">Protein in Urine [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams) newborn 4</t>
+          <t xml:space="preserve">Protein in Urine DMP</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams): [Delivery summary]</t>
+          <t xml:space="preserve">Ruptured Membranes [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birth Weight (grams)</t>
+          <t xml:space="preserve">Ruptured Membranes DMP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controlled Cord Traction (CCT): [Delivery summary]</t>
+          <t xml:space="preserve">Temperature (°C) [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controlled Cord Traction (CCT)</t>
+          <t xml:space="preserve">Temperature (°C) DMP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delivery summary</t>
+          <t xml:space="preserve">Delivery Monitoring partograph</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Delivery: [Delivery summary]</t>
+          <t xml:space="preserve">Time of Admission [Delivery Monitoring partograph]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Delivery</t>
+          <t xml:space="preserve">Time of Admission DMP</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episiotomy performed: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 10th min [Delivery summary]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episiotomy performed</t>
+          <t xml:space="preserve">Apgar Score 10th min</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding Option [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding Option</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 2</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestation: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestation</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 3</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Result: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Result</t>
+          <t xml:space="preserve">Apgar Score 10th min newborn 4</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Testing Accepted: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 1st min [Delivery summary]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Testing Accepted</t>
+          <t xml:space="preserve">Apgar Score 1st min</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, specify facility or service: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">If yes, specify facility or service</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 2</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laceration Repair: [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laceration Repair</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 3</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Removal of Placenta (MRP) [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Removal of Placenta (MRP)</t>
+          <t xml:space="preserve">Apgar Score 1st min newborn 4</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measures Taken [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 5th min [Delivery summary]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measures Taken</t>
+          <t xml:space="preserve">Apgar Score 5th min</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother and newborn referred for care/support? [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mother and newborn referred for care/support</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 2</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 3</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 2 [Delivery summary]</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 2</t>
+          <t xml:space="preserve">Apgar Score 5th min newborn 4</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 3 [Delivery summary]</t>
+          <t xml:space="preserve">ARV Px for Newborn (by type): [Delivery summary]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 3</t>
+          <t xml:space="preserve">ARV Px for Newborn</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 4 [Delivery summary]</t>
+          <t xml:space="preserve">ARV Rx for Mother: (by type) [Delivery summary]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 4</t>
+          <t xml:space="preserve">ARV Rx for Mother</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Newborns: [Delivery summary]</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 2: [Delivery summary]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Newborns</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 2</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obstetric condition at delivery [Delivery summary]</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 3: [Delivery summary]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obstetric condition at delivery</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 3</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Status [Delivery summary]</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 4: [Delivery summary]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Status</t>
+          <t xml:space="preserve">Birth Weight (grams) newborn 4</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex [Delivery summary]</t>
+          <t xml:space="preserve">Birth Weight (grams): [Delivery summary]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex</t>
+          <t xml:space="preserve">Birth Weight (grams)</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 2 [Delivery summary]</t>
+          <t xml:space="preserve">Controlled Cord Traction (CCT): [Delivery summary]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 2</t>
+          <t xml:space="preserve">Controlled Cord Traction (CCT)</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 3 [Delivery summary]</t>
+          <t xml:space="preserve">Date of Delivery: [Delivery summary]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 3</t>
+          <t xml:space="preserve">Date of Delivery</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 4 [Delivery summary]</t>
+          <t xml:space="preserve">Episiotomy performed: [Delivery summary]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sex newborn 4</t>
+          <t xml:space="preserve">Episiotomy performed</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 2: [Delivery summary]</t>
+          <t xml:space="preserve">Feeding Option [Delivery summary]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 2</t>
+          <t xml:space="preserve">Feeding Option</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 3: [Delivery summary]</t>
+          <t xml:space="preserve">Gestation: [Delivery summary]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 3</t>
+          <t xml:space="preserve">Gestation</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 4: [Delivery summary]</t>
+          <t xml:space="preserve">HIV Result: [Delivery summary]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth newborn 4</t>
+          <t xml:space="preserve">HIV Result</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth: [Delivery summary]</t>
+          <t xml:space="preserve">HIV Testing Accepted: [Delivery summary]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth</t>
+          <t xml:space="preserve">HIV Testing Accepted</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Delivery: [Delivery summary]</t>
+          <t xml:space="preserve">If yes, specify facility or service: [Delivery summary]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of Delivery:</t>
+          <t xml:space="preserve">If yes, specify facility or service</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterotonics given [Delivery summary]</t>
+          <t xml:space="preserve">Laceration Repair: [Delivery summary]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterotonics given</t>
+          <t xml:space="preserve">Laceration Repair</t>
         </is>
       </c>
     </row>
@@ -1004,3121 +1004,5620 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vacuum/Forceps [Delivery summary]</t>
+          <t xml:space="preserve">Length (cm): [Delivery summary]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vacuum/Forceps</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brief History [Discharge Summary]</t>
+          <t xml:space="preserve">Manual Removal of Placenta (MRP) [Delivery summary]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brief History</t>
+          <t xml:space="preserve">Manual Removal of Placenta (MRP)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Findings [Discharge Summary]</t>
+          <t xml:space="preserve">Measures Taken [Delivery summary]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Findings</t>
+          <t xml:space="preserve">Measures Taken</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition of Discharge [Discharge Summary]</t>
+          <t xml:space="preserve">Mode of Delivery [Delivery summary]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition of Discharge</t>
+          <t xml:space="preserve">Mode of Delivery maternal</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Course of treatment [Discharge Summary]</t>
+          <t xml:space="preserve">Mother and newborn referred for care/support? [Delivery summary]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Course of treatment</t>
+          <t xml:space="preserve">Mother and newborn referred for care/support</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Admission [Discharge Summary]</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions [Delivery summary]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Admission</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Discharge [Discharge Summary]</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of Discharge</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final Diagnosis [Discharge Summary]</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final Diagnosis</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Findings [Discharge Summary]</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Findings</t>
+          <t xml:space="preserve">Newborn Immunizations and Interventions newborn 4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan at Discharge [Discharge Summary]</t>
+          <t xml:space="preserve">Number of Newborns: [Delivery summary]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan at Discharge</t>
+          <t xml:space="preserve">Number of Newborns</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discharge Summary</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedures [Discharge Summary]</t>
+          <t xml:space="preserve">Obstetric condition at delivery [Delivery summary]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedures</t>
+          <t xml:space="preserve">Obstetric condition at delivery</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr breakfast [DM followup chart]</t>
+          <t xml:space="preserve">Other specify [Delivery summary]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr breakfast</t>
+          <t xml:space="preserve">Other Number of Newborns</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr dinner [DM followup chart]</t>
+          <t xml:space="preserve">Outcome [Delivery summary]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr dinner</t>
+          <t xml:space="preserve">birth outcome</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr lunch [DM followup chart]</t>
+          <t xml:space="preserve">Outcome of newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 hr lunch</t>
+          <t xml:space="preserve">birth outcome newborn 2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr breakfast [DM followup chart]</t>
+          <t xml:space="preserve">Outcome of newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr breakfast</t>
+          <t xml:space="preserve">birth outcome newborn 3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr dinner [DM followup chart]</t>
+          <t xml:space="preserve">Outcome of newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr dinner</t>
+          <t xml:space="preserve">birth outcome newborn 4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr lunch [DM followup chart]</t>
+          <t xml:space="preserve">Placenta Status [Delivery summary]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2hr lunch</t>
+          <t xml:space="preserve">Placenta Status</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dose of insulin/40% if needed [DM followup chart]</t>
+          <t xml:space="preserve">Sex [Delivery summary]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dose of insulin/40% if needed</t>
+          <t xml:space="preserve">Sex</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">DM followup chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">FBS [DM followup chart]</t>
+          <t xml:space="preserve">Sex newborn 2 [Delivery summary]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">FBS</t>
+          <t xml:space="preserve">Sex newborn 2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bishop score (for induction) [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Sex newborn 3 [Delivery summary]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bishop score for induction IA</t>
+          <t xml:space="preserve">Sex newborn 3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP (diastolic) [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Sex newborn 4 [Delivery summary]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP diastolic IA</t>
+          <t xml:space="preserve">Sex newborn 4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP (systolic) [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Specify [Delivery summary]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP systolic IA</t>
+          <t xml:space="preserve">Obstetric condition at delivery Specify</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical status [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Stillbirth newborn 2: [Delivery summary]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical status IA</t>
+          <t xml:space="preserve">Stillbirth newborn 2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical status at decision (for augmentation) [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Stillbirth newborn 3: [Delivery summary]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical status at decision for augmentation IA</t>
+          <t xml:space="preserve">Stillbirth newborn 3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraction duration [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Stillbirth newborn 4: [Delivery summary]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraction duration IA</t>
+          <t xml:space="preserve">Stillbirth newborn 4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraction frequency [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Stillbirth: [Delivery summary]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraction frequency IA</t>
+          <t xml:space="preserve">Stillbirth</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of initiation [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Time of Delivery: [Delivery summary]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date of initiation IA</t>
+          <t xml:space="preserve">Time of Delivery:</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deciding physician for the procedure [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Uterotonics given [Delivery summary]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deciding physician for the procedure IA</t>
+          <t xml:space="preserve">Uterotonics given</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Delivery summary</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dose of Oxytocin [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Vacuum/Forceps [Delivery summary]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dose of Oxytocin IA</t>
+          <t xml:space="preserve">Vacuum/Forceps</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 1st dose [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Brief History [Discharge Summary]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 1st dose IA</t>
+          <t xml:space="preserve">Brief History</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 2nd dose [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Clinical Findings [Discharge Summary]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 2nd dose IA</t>
+          <t xml:space="preserve">Clinical Findings</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 3rd dose IA [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Condition of Discharge [Discharge Summary]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate in Drop/min 3rd dose IA</t>
+          <t xml:space="preserve">Condition of Discharge</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of initiation [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Course of treatment [Discharge Summary]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time of initiation IA</t>
+          <t xml:space="preserve">Course of treatment</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induction and augmentation chart</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of procedure [Induction and augmentation chart]</t>
+          <t xml:space="preserve">Date of Admission [Discharge Summary]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of procedure IA</t>
+          <t xml:space="preserve">Date of Admission</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bladder status [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Date of Discharge [Discharge Summary]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bladder status ID</t>
+          <t xml:space="preserve">Date of Discharge</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilation [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Final Diagnosis [Discharge Summary]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilation ID</t>
+          <t xml:space="preserve">Final Diagnosis</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forceps type used [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Lab Findings [Discharge Summary]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forceps type used ID</t>
+          <t xml:space="preserve">Lab Findings</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">GA after newborn assessment (wks) [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Plan at Discharge [Discharge Summary]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">GA after newborn assessment ID</t>
+          <t xml:space="preserve">Plan at Discharge</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">Discharge Summary</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference (cm) [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Procedures [Discharge Summary]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head circumference ID</t>
+          <t xml:space="preserve">Procedures</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrument used [Instrumental Delivery form]</t>
+          <t xml:space="preserve">1 hr breakfast [DM followup chart]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrument used ID</t>
+          <t xml:space="preserve">1 hr breakfast</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental delivery successful [Instrumental Delivery form]</t>
+          <t xml:space="preserve">1 hr dinner [DM followup chart]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental delivery successful ID</t>
+          <t xml:space="preserve">1 hr dinner</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental delivery? [Instrumental Delivery form]</t>
+          <t xml:space="preserve">1 hr lunch [DM followup chart]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental delivery</t>
+          <t xml:space="preserve">1 hr lunch</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonate referred to neonatology [Instrumental Delivery form]</t>
+          <t xml:space="preserve">2hr breakfast [DM followup chart]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neonate referred to neonatology ID</t>
+          <t xml:space="preserve">2hr breakfast</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn complication [Instrumental Delivery form]</t>
+          <t xml:space="preserve">2hr dinner [DM followup chart]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn complication ID</t>
+          <t xml:space="preserve">2hr dinner</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of pulls [Instrumental Delivery form]</t>
+          <t xml:space="preserve">2hr lunch [DM followup chart]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of pulls ID</t>
+          <t xml:space="preserve">2hr lunch</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presentation [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Date [DM followup chart]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presentation ID</t>
+          <t xml:space="preserve">Date insulin</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instrumental Delivery form</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vacuum type used [Instrumental Delivery form]</t>
+          <t xml:space="preserve">Dose of insulin/40% if needed [DM followup chart]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vacuum type used ID</t>
+          <t xml:space="preserve">Dose of insulin/40% if needed</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick chart</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kick chart event date [kick chart]</t>
+          <t xml:space="preserve">FBS [DM followup chart]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kick chart event date</t>
+          <t xml:space="preserve">FBS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick chart</t>
+          <t xml:space="preserve">DM followup chart</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count date [kick chart]</t>
+          <t xml:space="preserve">Time [DM followup chart]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count date</t>
+          <t xml:space="preserve">Time insulin</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick chart</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count end time [kick chart]</t>
+          <t xml:space="preserve">Bishop score (for induction) [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count end time</t>
+          <t xml:space="preserve">Bishop score for induction IA</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick chart</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count start time [kick chart]</t>
+          <t xml:space="preserve">BP (diastolic) [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick count start time</t>
+          <t xml:space="preserve">BP diastolic IA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">kick chart</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of kicks [kick chart]</t>
+          <t xml:space="preserve">BP (systolic) [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of kicks</t>
+          <t xml:space="preserve">BP systolic IA</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labour Management</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episiothomy [Labour Management]</t>
+          <t xml:space="preserve">Cervical status [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episiothomy</t>
+          <t xml:space="preserve">Cervical status IA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labour Management</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fetal distress [Labour Management]</t>
+          <t xml:space="preserve">Cervical status at decision (for augmentation) [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fetal distress</t>
+          <t xml:space="preserve">Cervical status at decision for augmentation IA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labour Management</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indication [Labour Management]</t>
+          <t xml:space="preserve">Contraction duration [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indication</t>
+          <t xml:space="preserve">Contraction duration IA</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labour Management</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of delivery [Labour Management]</t>
+          <t xml:space="preserve">Contraction frequency [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mode of delivery</t>
+          <t xml:space="preserve">Contraction frequency IA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latent Phase followup</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilatation [Latent Phase followup]</t>
+          <t xml:space="preserve">Date [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilatation LPF</t>
+          <t xml:space="preserve">Date IA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latent Phase followup</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical effacement [Latent Phase followup]</t>
+          <t xml:space="preserve">Date of initiation [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical effacement LPF</t>
+          <t xml:space="preserve">Date of initiation IA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latent Phase followup</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colour of Liquor [Latent Phase followup]</t>
+          <t xml:space="preserve">Deciding physician for the procedure [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colour of Liquor LPF</t>
+          <t xml:space="preserve">Deciding physician for the procedure IA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latent Phase followup</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine contraction [Latent Phase followup]</t>
+          <t xml:space="preserve">Dose [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine contraction LPF</t>
+          <t xml:space="preserve">Dose IA</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC Contact [Maternal History]</t>
+          <t xml:space="preserve">Dose of Oxytocin [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANC Contact</t>
+          <t xml:space="preserve">Dose of Oxytocin IA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Co-existing Medical Complications [Maternal History]</t>
+          <t xml:space="preserve">FHB (Fetal Heart Beat) [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Co-existing Medical Complications</t>
+          <t xml:space="preserve">FHB IA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Gestational Age (From early ultrasound in weeks) [Maternal History]</t>
+          <t xml:space="preserve">Indication [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational Age (From early ultrasound in weeks)</t>
+          <t xml:space="preserve">Indication IA</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current Gestational Age (From LMP in weeks) [Maternal History]</t>
+          <t xml:space="preserve">PR [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational Age (From LMP in weeks)</t>
+          <t xml:space="preserve">PR IA</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early Ultrasound Date [Maternal History]</t>
+          <t xml:space="preserve">Rate in Drop/min 1st dose [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Early Ultrasound Date</t>
+          <t xml:space="preserve">Rate in Drop/min 1st dose IA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDD (based on early ultrasound date) [Maternal History]</t>
+          <t xml:space="preserve">Rate in Drop/min 2nd dose [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDD based on early ultrasound date</t>
+          <t xml:space="preserve">Rate in Drop/min 2nd dose IA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDD [Maternal History]</t>
+          <t xml:space="preserve">Rate in Drop/min 3rd dose IA [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDD</t>
+          <t xml:space="preserve">Rate in Drop/min 3rd dose IA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational Age at early ultrasound (weeks) [Maternal History]</t>
+          <t xml:space="preserve">Temp [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestational Age at early ultrasound</t>
+          <t xml:space="preserve">Temp IA</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravida [Maternal History]</t>
+          <t xml:space="preserve">Time [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravida</t>
+          <t xml:space="preserve">Time IA</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of Abortion [Maternal History]</t>
+          <t xml:space="preserve">Time of initiation [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of Abortion</t>
+          <t xml:space="preserve">Time of initiation IA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Induction and augmentation chart</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of Ectopic Pregnancy [Maternal History]</t>
+          <t xml:space="preserve">Type of procedure [Induction and augmentation chart]</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of Ectopic Pregnancy</t>
+          <t xml:space="preserve">Type of procedure IA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of GTD [Maternal History]</t>
+          <t xml:space="preserve">Bladder status [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">History of GTD</t>
+          <t xml:space="preserve">Bladder status ID</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induced [Maternal History]</t>
+          <t xml:space="preserve">Cap size [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Induced</t>
+          <t xml:space="preserve">Cap size ID</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP Date [Maternal History]</t>
+          <t xml:space="preserve">Caput [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP Date</t>
+          <t xml:space="preserve">Caput ID</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP known? [Maternal History]</t>
+          <t xml:space="preserve">Cervical dilation [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNMP known</t>
+          <t xml:space="preserve">Cervical dilation ID</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of ANC contacts [Maternal History]</t>
+          <t xml:space="preserve">Date [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of ANC contacts</t>
+          <t xml:space="preserve">Date of instrumental delivery</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Previous Abortions [Maternal History]</t>
+          <t xml:space="preserve">Duration (min) [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Previous Abortions</t>
+          <t xml:space="preserve">Duration ID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parity [Maternal History]</t>
+          <t xml:space="preserve">Forceps type used [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parity</t>
+          <t xml:space="preserve">Forceps type used ID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past obstetric complications [Maternal History]</t>
+          <t xml:space="preserve">GA after newborn assessment (wks) [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Past obstetric complications</t>
+          <t xml:space="preserve">GA after newborn assessment ID</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of ANC Visit [Maternal History]</t>
+          <t xml:space="preserve">Head circumference (cm) [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place of ANC Visit</t>
+          <t xml:space="preserve">Head circumference ID</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presenting Complaint: [Maternal History]</t>
+          <t xml:space="preserve">Indication [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presenting Complaint</t>
+          <t xml:space="preserve">Indication ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provisions at the ANC [Maternal History]</t>
+          <t xml:space="preserve">Instrument used [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provisions at the ANC</t>
+          <t xml:space="preserve">Instrument used ID</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maternal History</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spontaneous [Maternal History]</t>
+          <t xml:space="preserve">Instrumental delivery successful [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spontaneous</t>
+          <t xml:space="preserve">Instrumental delivery successful ID</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allergy [Medication Administration record]</t>
+          <t xml:space="preserve">Instrumental delivery? [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allergy</t>
+          <t xml:space="preserve">Instrumental delivery</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagnosis [Medication Administration record]</t>
+          <t xml:space="preserve">Live birth [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagnosis</t>
+          <t xml:space="preserve">Live birth ID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Adminstration route [Medication Administration record]</t>
+          <t xml:space="preserve">Molding [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Adminstration route</t>
+          <t xml:space="preserve">Molding ID</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication frequency [Medication Administration record]</t>
+          <t xml:space="preserve">Neonate referred to neonatology [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication frequency</t>
+          <t xml:space="preserve">Neonate referred to neonatology ID</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication given by [Medication Administration record]</t>
+          <t xml:space="preserve">Newborn complication [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication given by</t>
+          <t xml:space="preserve">Newborn complication ID</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication name [Medication Administration record]</t>
+          <t xml:space="preserve">Number of pulls [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication name</t>
+          <t xml:space="preserve">Number of pulls ID</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication Administration record</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time to be given [Medication Administration record]</t>
+          <t xml:space="preserve">Position [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time to be given</t>
+          <t xml:space="preserve">Position ID</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">MGSO4 follow up</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">If convulsion Re occur/15min dose [MGSO4 follow up]</t>
+          <t xml:space="preserve">Presentation [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">If convulsion Re occur/15min dose mgso4</t>
+          <t xml:space="preserve">Presentation ID</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">MGSO4 follow up</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maintenance Post delivery dose [MGSO4 follow up]</t>
+          <t xml:space="preserve">Sex [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maintenance Post delivery dose mgso4</t>
+          <t xml:space="preserve">Sex ID</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">MGSO4 follow up</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">MGSO4 Followup event date [MGSO4 follow up]</t>
+          <t xml:space="preserve">Station [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">MGSO4 Followup event date</t>
+          <t xml:space="preserve">Station ID</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admission Diagnosis [Pain Management]</t>
+          <t xml:space="preserve">Stillbirth [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admission Diagnosis PM</t>
+          <t xml:space="preserve">Stillbirth ID</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breastfeeding [Pain Management]</t>
+          <t xml:space="preserve">Time [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breastfeeding PM</t>
+          <t xml:space="preserve">Time of instrumental delivery</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catheterized [Pain Management]</t>
+          <t xml:space="preserve">Vacuum type used [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catheterized PM</t>
+          <t xml:space="preserve">Vacuum type used ID</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">Instrumental Delivery form</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foul smelling discharge [Pain Management]</t>
+          <t xml:space="preserve">Weight (gm) [Instrumental Delivery form]</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foul smelling discharge PM</t>
+          <t xml:space="preserve">Weight ID</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">kick chart</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fundal height [Pain Management]</t>
+          <t xml:space="preserve">Kick chart event date [kick chart]</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fundal height PM</t>
+          <t xml:space="preserve">Kick chart event date</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">kick chart</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modified pain score [Pain Management]</t>
+          <t xml:space="preserve">kick count date [kick chart]</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modified pain score PM</t>
+          <t xml:space="preserve">kick count date</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">kick chart</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain managed with [Pain Management]</t>
+          <t xml:space="preserve">kick count end time [kick chart]</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain managed with PM</t>
+          <t xml:space="preserve">kick count end time</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">kick chart</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature [Pain Management]</t>
+          <t xml:space="preserve">kick count start time [kick chart]</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature PM</t>
+          <t xml:space="preserve">kick count start time</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">kick chart</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine conted [Pain Management]</t>
+          <t xml:space="preserve">Number of kicks [kick chart]</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine conted PM</t>
+          <t xml:space="preserve">Number of kicks</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pain Management</t>
+          <t xml:space="preserve">Labour Management</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal bleeding [Pain Management]</t>
+          <t xml:space="preserve">Episiothomy [Labour Management]</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal bleeding PM</t>
+          <t xml:space="preserve">Episiothomy</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Labour Management</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure (Diastolic) [Physical Examination]</t>
+          <t xml:space="preserve">Fetal distress [Labour Management]</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure Diastolic</t>
+          <t xml:space="preserve">Fetal distress</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Labour Management</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure (Systolic) [Physical Examination]</t>
+          <t xml:space="preserve">Indication [Labour Management]</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure Systolic</t>
+          <t xml:space="preserve">Indication</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Labour Management</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status: Dilatation [Physical Examination]</t>
+          <t xml:space="preserve">Mode of delivery [Labour Management]</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status Dilatation</t>
+          <t xml:space="preserve">Mode of delivery</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Labour Management</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status: Effacement [Physical Examination]</t>
+          <t xml:space="preserve">Other [Labour Management]</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status Effacement</t>
+          <t xml:space="preserve">Indication other</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status: Position [Physical Examination]</t>
+          <t xml:space="preserve">BP (diastolic) [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status Position</t>
+          <t xml:space="preserve">BP diastolic LPF</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status: Station [Physical Examination]</t>
+          <t xml:space="preserve">BP (systolic) [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical Status Station</t>
+          <t xml:space="preserve">BP systolic LPF</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest [Physical Examination]</t>
+          <t xml:space="preserve">Cervical dilatation [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest</t>
+          <t xml:space="preserve">Cervical dilatation LPF</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical pelvimetry [Physical Examination]</t>
+          <t xml:space="preserve">Cervical effacement [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical pelvimetry</t>
+          <t xml:space="preserve">Cervical effacement LPF</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNS [Physical Examination]</t>
+          <t xml:space="preserve">Colour of Liquor [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">CNS</t>
+          <t xml:space="preserve">Colour of Liquor LPF</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVA tenderness [Physical Examination]</t>
+          <t xml:space="preserve">Date [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVA tenderness</t>
+          <t xml:space="preserve">Date LPF</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVS [Physical Examination]</t>
+          <t xml:space="preserve">FHB (Fetal Heart Beat) [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVS</t>
+          <t xml:space="preserve">FHB LPF</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration [Physical Examination]</t>
+          <t xml:space="preserve">HCT [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t xml:space="preserve">HCT LPF</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ears: [Physical Examination]</t>
+          <t xml:space="preserve">PR [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ears</t>
+          <t xml:space="preserve">PR LPF</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eyes: [Physical Examination]</t>
+          <t xml:space="preserve">RR [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eyes</t>
+          <t xml:space="preserve">RR LPF</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">FHB [Physical Examination]</t>
+          <t xml:space="preserve">Temp [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">FHB</t>
+          <t xml:space="preserve">Temp LPF</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frequency [Physical Examination]</t>
+          <t xml:space="preserve">Time [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frequency</t>
+          <t xml:space="preserve">Time LPF</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Latent Phase followup</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">GCS [Physical Examination]</t>
+          <t xml:space="preserve">Uterine contraction [Latent Phase followup]</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">GCS</t>
+          <t xml:space="preserve">Uterine contraction LPF</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head: [Physical Examination]</t>
+          <t xml:space="preserve">ANC Contact [Maternal History]</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Head</t>
+          <t xml:space="preserve">ANC Contact</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">IS/MSS [Physical Examination]</t>
+          <t xml:space="preserve">Cesarean delivery [Maternal History]</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">IS/MSS</t>
+          <t xml:space="preserve">Number of cesarean delivery</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">LGS [Physical Examination]</t>
+          <t xml:space="preserve">Co-existing Medical Complications [Maternal History]</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">LGS</t>
+          <t xml:space="preserve">Co-existing Medical Complications</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lie [Physical Examination]</t>
+          <t xml:space="preserve">Current Gestational Age (From early ultrasound in weeks) [Maternal History]</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lie</t>
+          <t xml:space="preserve">Gestational Age (From early ultrasound in weeks)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meconium [Physical Examination]</t>
+          <t xml:space="preserve">Current Gestational Age (From LMP in weeks) [Maternal History]</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meconium</t>
+          <t xml:space="preserve">Gestational Age (From LMP in weeks)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane Status [Physical Examination]</t>
+          <t xml:space="preserve">Early Ultrasound Date [Maternal History]</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane Status</t>
+          <t xml:space="preserve">Early Ultrasound Date</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nose: [Physical Examination]</t>
+          <t xml:space="preserve">EDD (based on early ultrasound date) [Maternal History]</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nose</t>
+          <t xml:space="preserve">EDD based on early ultrasound date</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Pregnancy Weight (Kg) [Physical Examination]</t>
+          <t xml:space="preserve">EDD [Maternal History]</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Pregnancy Weight</t>
+          <t xml:space="preserve">EDD</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presentation [Physical Examination]</t>
+          <t xml:space="preserve">Gestational Age at early ultrasound (weeks) [Maternal History]</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presentation</t>
+          <t xml:space="preserve">Gestational Age at early ultrasound</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raptured [Physical Examination]</t>
+          <t xml:space="preserve">Gravida [Maternal History]</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raptured</t>
+          <t xml:space="preserve">Gravida</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFH [Physical Examination]</t>
+          <t xml:space="preserve">History of Abortion [Maternal History]</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFH</t>
+          <t xml:space="preserve">History of Abortion</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature (°C) [Physical Examination]</t>
+          <t xml:space="preserve">History of Ectopic Pregnancy [Maternal History]</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature</t>
+          <t xml:space="preserve">History of Ectopic Pregnancy</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throat: [Physical Examination]</t>
+          <t xml:space="preserve">History of GTD [Maternal History]</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throat</t>
+          <t xml:space="preserve">History of GTD</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin A FHB [Physical Examination]</t>
+          <t xml:space="preserve">Induced [Maternal History]</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin A FHB</t>
+          <t xml:space="preserve">Induced</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin A Presentation [Physical Examination]</t>
+          <t xml:space="preserve">LNMP Date [Maternal History]</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin A Presentation</t>
+          <t xml:space="preserve">LNMP Date</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin B FHB [Physical Examination]</t>
+          <t xml:space="preserve">LNMP known? [Maternal History]</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin B FHB</t>
+          <t xml:space="preserve">LNMP known</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin B Presentation [Physical Examination]</t>
+          <t xml:space="preserve">Number of ANC contacts [Maternal History]</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin B Presentation</t>
+          <t xml:space="preserve">Number of ANC contacts</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin? [Physical Examination]</t>
+          <t xml:space="preserve">Number of Previous Abortions [Maternal History]</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Twin</t>
+          <t xml:space="preserve">Number of Previous Abortions</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical Examination</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine Contractions in 10 min [Physical Examination]</t>
+          <t xml:space="preserve">Operative vaginal delivery [Maternal History]</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterine Contractions in 10 min</t>
+          <t xml:space="preserve">Number of Operative vaginal delivery</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action Taken [Postpartum care]</t>
+          <t xml:space="preserve">Other [Maternal History]</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action Taken pp</t>
+          <t xml:space="preserve">Place of ANC Visit other</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARV Rx for Mother (By type) [Postpartum care]</t>
+          <t xml:space="preserve">Parity [Maternal History]</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARV Rx for Mother (By type) pp</t>
+          <t xml:space="preserve">Parity</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARV Rx for Newborn (By type) [Postpartum care]</t>
+          <t xml:space="preserve">Past obstetric complications [Maternal History]</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARV Rx for Newborn (By type) pp</t>
+          <t xml:space="preserve">Past obstetric complications</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby Breastfeeding [Postpartum care]</t>
+          <t xml:space="preserve">Place of ANC Visit [Maternal History]</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby Breastfeeding pp</t>
+          <t xml:space="preserve">Place of ANC Visit</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby Breathing Well [Postpartum care]</t>
+          <t xml:space="preserve">Presenting Complaint: [Maternal History]</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baby Breathing Well pp</t>
+          <t xml:space="preserve">Presenting Complaint</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure (BP) [Postpartum care]</t>
+          <t xml:space="preserve">Provisions at the ANC [Maternal History]</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blood Pressure pp</t>
+          <t xml:space="preserve">Provisions at the ANC</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breast Exam [Postpartum care]</t>
+          <t xml:space="preserve">Remaining Current Gestational Age (From early ultrasound in days) [Maternal History]</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breast Exam pp</t>
+          <t xml:space="preserve">Gestational Age remaining(From early ultrasound in days)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dribbling / Leaking Urine [Postpartum care]</t>
+          <t xml:space="preserve">Remaining Gestational Age (From LMP in days) [Maternal History]</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dribbling / Leaking Urine pp</t>
+          <t xml:space="preserve">Gestational Age (From LMP in days)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding Option [Postpartum care]</t>
+          <t xml:space="preserve">Remaining Gestational Age at early ultrasound (days) [Maternal History]</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeding Option pp</t>
+          <t xml:space="preserve">Gestational Age at early ultrasound remaining days</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">FP Counseling and Method Provided [Postpartum care]</t>
+          <t xml:space="preserve">Spcify Other [Maternal History]</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">FP Counseling and Method Provided pp</t>
+          <t xml:space="preserve">Co-existing Medical Complications Others Specify</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Test Result [Postpartum care]</t>
+          <t xml:space="preserve">Specify Other [Maternal History]</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIV Test Result pp</t>
+          <t xml:space="preserve">past obstetric complications other specify</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">IFA Supplement Given [Postpartum care]</t>
+          <t xml:space="preserve">Spontaneous [Maternal History]</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">IFA Supplement Given pp</t>
+          <t xml:space="preserve">Spontaneous</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Maternal History</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immunization (BCG) [Postpartum care]</t>
+          <t xml:space="preserve">SVD [Maternal History]</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immunization (BCG) pp</t>
+          <t xml:space="preserve">Number of SVD</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Referred to Chronic HIV Infant Care [Postpartum care]</t>
+          <t xml:space="preserve">Allergy [Medication Administration record]</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newborn Referred to Chronic HIV Infant Care pp</t>
+          <t xml:space="preserve">Allergy</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterus Contracted / Look for PPH [Postpartum care]</t>
+          <t xml:space="preserve">Date [Medication Administration record]</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uterus Contracted / Look for PPH pp</t>
+          <t xml:space="preserve">Medication prescription date</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postpartum care</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal Discharge (After 4 wks of delivery) [Postpartum care]</t>
+          <t xml:space="preserve">Diagnosis [Medication Administration record]</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vaginal Discharge (After 4 wks of delivery) pp</t>
+          <t xml:space="preserve">Diagnosis</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIOPHYSICAL PROFILE [PREECLAMPSIA  CHART]</t>
+          <t xml:space="preserve">Medication Adminstration route [Medication Administration record]</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIOPHYSICAL PROFILE PECL</t>
+          <t xml:space="preserve">Medication Adminstration route</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preeclampsia event date [PREECLAMPSIA  CHART]</t>
+          <t xml:space="preserve">Medication frequency [Medication Administration record]</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preeclampsia event date</t>
+          <t xml:space="preserve">Medication frequency</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROM chart</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foul smelling discharge [PROM chart]</t>
+          <t xml:space="preserve">Medication given by [Medication Administration record]</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foul smelling discharge PROM</t>
+          <t xml:space="preserve">Medication given by</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROM chart</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROM event date [PROM chart]</t>
+          <t xml:space="preserve">Medication name [Medication Administration record]</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROM event date</t>
+          <t xml:space="preserve">Medication name</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">Medication Administration record</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adherent Clot? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Time to be given [Medication Administration record]</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adherent Clot</t>
+          <t xml:space="preserve">Time to be given</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arteries [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">BP [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arteries</t>
+          <t xml:space="preserve">BP mgso4</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cord Around Body? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Dose [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cord Around Body</t>
+          <t xml:space="preserve">Dose for LOADING Dose 14GM mgso4</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cord insertion central? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Drug Type/Name [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">cord insertion central</t>
+          <t xml:space="preserve">Drug type mgso4</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">If No, amount apparently missing: [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">DTR [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">If No, amount apparently missing</t>
+          <t xml:space="preserve">DTR mgso4</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Yes, approximate area affected: [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">If convulsion Re occur/15min dose [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Yes, approximate area affected</t>
+          <t xml:space="preserve">If convulsion Re occur/15min dose mgso4</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knots Present? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Injection Site [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knots Present</t>
+          <t xml:space="preserve">Injection Site mgso4</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Vessels [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Maintenance dose [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of Vessels</t>
+          <t xml:space="preserve">Maintenance dose mgso4</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Complete? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Maintenance Post delivery dose [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Complete</t>
+          <t xml:space="preserve">Maintenance Post delivery dose mgso4</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Shape [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">MGSO4 Followup event date [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placenta Shape</t>
+          <t xml:space="preserve">MGSO4 Followup event date</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrombosis Observed? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">remark [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrombosis Observed</t>
+          <t xml:space="preserve">remark mgso4</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vein [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">Route given [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vein</t>
+          <t xml:space="preserve">Route given mgso4</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stillbirth Evaluation</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wharton’s Jelly present? [Stillbirth Evaluation]</t>
+          <t xml:space="preserve">RR [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wharton’s Jelly present</t>
+          <t xml:space="preserve">RR mgso4</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLAC CHART</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Tenderness [TOLAC CHART]</t>
+          <t xml:space="preserve">Staff name [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abdominal Tenderness VBAC</t>
+          <t xml:space="preserve">Staff name mgso4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLAC CHART</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilatation [TOLAC CHART]</t>
+          <t xml:space="preserve">Time Given [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cervical dilatation VBAC</t>
+          <t xml:space="preserve">Time given mgso4</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOLAC CHART</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolac event date [TOLAC CHART]</t>
+          <t xml:space="preserve">Time Next [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolac event date</t>
+          <t xml:space="preserve">Time next mgso4</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">MGSO4 follow up</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">age</t>
+          <t xml:space="preserve">UOP Q 4hrs [MGSO4 follow up]</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Age</t>
+          <t xml:space="preserve">UOP Q 4hrs mgso4</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">Admission Diagnosis [Pain Management]</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">MRN</t>
+          <t xml:space="preserve">Admission Diagnosis PM</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">education_details</t>
+          <t xml:space="preserve">BP [Pain Management]</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education level</t>
+          <t xml:space="preserve">BP PM</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">occupation</t>
+          <t xml:space="preserve">Breastfeeding [Pain Management]</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Occupation</t>
+          <t xml:space="preserve">Breastfeeding PM</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">first_name</t>
+          <t xml:space="preserve">Catheterized [Pain Management]</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers First Name</t>
+          <t xml:space="preserve">Catheterized PM</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">family_name</t>
+          <t xml:space="preserve">Cord tie [Pain Management]</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers Father Name</t>
+          <t xml:space="preserve">Cord tie PM</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">family_name</t>
+          <t xml:space="preserve">Date [Pain Management]</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers Grandfather Name</t>
+          <t xml:space="preserve">Date PM</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracked Entity Attributes</t>
+          <t xml:space="preserve">Pain Management</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">address1</t>
+          <t xml:space="preserve">Foul smelling discharge [Pain Management]</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mothers adress</t>
+          <t xml:space="preserve">Foul smelling discharge PM</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fundal height [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fundal height PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modified pain score [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modified pain score PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain managed with [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain managed with PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine conted [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine conted PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain Management</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal bleeding [Pain Management]</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal bleeding PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure (Diastolic) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure Diastolic</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure (Systolic) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure Systolic</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BMI [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers BMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status: Dilatation [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status Dilatation</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status: Effacement [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status Effacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status: Position [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status: Station [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical Status Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chest [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chest</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clinical pelvimetry [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clinical pelvimetry</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNS [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVA tenderness [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVA tenderness</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVS [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CVS</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ears: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ears</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eyes: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eyes</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frequency [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GCS [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Height (cm) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Height</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IS/MSS [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IS/MSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGS [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lie [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lie</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meconium [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meconium</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Membrane Status [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Membrane Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUAC (cm) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nose: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nose</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxygen saturation [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-Pregnancy Weight (Kg) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-Pregnancy Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presentation [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pulse Rate: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raptured [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raptured</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respiration Rate: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SFH [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SFH</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature (°C) [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Throat: [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Throat</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin A FHB [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin A FHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin A Presentation [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin A Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin B FHB [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin B FHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin B Presentation [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin B Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin? [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twin</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physical Examination</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine Contractions in 10 min [Physical Examination]</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine Contractions in 10 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action Taken [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action Taken pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anemia [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anemia pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARV Rx for Mother (By type) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARV Rx for Mother (By type) pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARV Rx for Newborn (By type) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARV Rx for Newborn (By type) pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Breastfeeding [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Breastfeeding pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Breathing Well [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Breathing Well pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Weight (grams) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baby Weight pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure (BP) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blood Pressure pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breast Exam [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breast Exam pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counseling Danger sign, FP, Hygiene, Nutrition, EPI, use of ITN, BF, HTP, etc [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counseling Provided pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date/stay [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date/stay pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dribbling / Leaking Urine [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dribbling / Leaking Urine pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeding Option [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeding Option pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FP Counseling and Method Provided [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FP Counseling and Method Provided pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIV Test Result [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIV Test Result pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIV Tested [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIV Tested pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IFA Supplement Given [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IFA Supplement Given pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Immunization (BCG) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Immunization (BCG) pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newborn Referred to Chronic HIV Infant Care [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newborn Referred to Chronic HIV Infant Care pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic Exam (if vaginal discharge) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic Exam pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/RR [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/RR pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterus Contracted / Look for PPH [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterus Contracted / Look for PPH pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpartum care</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal Discharge (After 4 wks of delivery) [Postpartum care]</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal Discharge (After 4 wks of delivery) pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIOPHYSICAL PROFILE [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIOPHYSICAL PROFILE PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (diastolic) [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP diastolic PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (systolic) [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP systolic PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulerd vision [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulerd vision PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DTR [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DTR PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epigastric pain [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epigastric pain PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB (Fetal Heart Beat) [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headache [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headache PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preeclampsia event date [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preeclampsia event date</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREECLAMPSIA  CHART</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP [PREECLAMPSIA  CHART]</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UOP PECL</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fhr [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fhr PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foul smelling discharge [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foul smelling discharge PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain scoring [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pain scoring PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM event date [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM event date</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine tenderness [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uterine tenderness PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROM chart</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wbc [PROM chart]</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wbc PROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adherent Clot? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adherent Clot</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arteries [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Around Body? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Around Body</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord insertion central? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cord insertion central</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Length (in cm) [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of Delivery: [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of stillbirth delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If No, amount apparently missing: [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If No, amount apparently missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Yes, approximate area affected: [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Yes, approximate area affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Yes, describe: [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Yes Thrombosis, describe</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knots Present? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knots Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of Delivery [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode of stillbirth delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of Vessels [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of Vessels</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placenta Complete? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placenta Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placenta Shape [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placenta Shape</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Diameter (in cm) [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Diameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Thickness (in cm) [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Weight (in gm) [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placental Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thrombosis Observed? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thrombosis Observed</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time stillbirth</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vein [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stillbirth Evaluation</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wharton’s Jelly present? [Stillbirth Evaluation]</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wharton’s Jelly present</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdominal Tenderness [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abdominal Tenderness VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (diastolic) [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP diastolic VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (systolic) [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP systolic VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical dilatation [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cervical dilatation VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contraction (Type) [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contraction Type VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB (Fetal Heart Beat) [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FHB VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RR VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Station [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Station VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tolac event date [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tolac event date</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOLAC CHART</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal bleeding [TOLAC CHART]</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaginal bleeding VBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tracked Entity Attributes</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address1</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers adress</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">age</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Age</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">education_details</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education level</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family_name</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers Father Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family_name</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers Grandfather Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">first_name</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mothers First Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occupation</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Occupation</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracked Entity Attributes</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
         <is>
           <t xml:space="preserve">primary_contact</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t xml:space="preserve">Mothers phone number</t>
         </is>
